--- a/Unity/Assets/Config/Excel/SkillAugmentOptionsConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillAugmentOptionsConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>##var</t>
   </si>
@@ -40,22 +40,10 @@
     <t>Id</t>
   </si>
   <si>
-    <t>Cost1</t>
-  </si>
-  <si>
     <t>SkillAugmentIds1</t>
   </si>
   <si>
-    <t>Cost2</t>
-  </si>
-  <si>
     <t>SkillAugmentIds2</t>
-  </si>
-  <si>
-    <t>Cost3</t>
-  </si>
-  <si>
-    <t>SkillAugmentIds3</t>
   </si>
   <si>
     <t>##type</t>
@@ -64,37 +52,28 @@
     <t>int#ref=SkillConfigCategory</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>(array#sep=,),int#ref=SkillAugmentConfigCategory</t>
   </si>
   <si>
     <t>##</t>
   </si>
   <si>
-    <t>升级消耗</t>
+    <t>第1个技能增幅Ids</t>
   </si>
   <si>
-    <t>1级技能增幅Ids</t>
+    <t>第2个技能增幅Ids</t>
   </si>
   <si>
-    <t>2级技能增幅Ids</t>
+    <t>101000111,101000112</t>
   </si>
   <si>
-    <t>3级技能增幅Ids</t>
+    <t>101000121,101000122,101000123</t>
   </si>
   <si>
-    <t>101000121,101000122</t>
+    <t>101001111,101001112</t>
   </si>
   <si>
-    <t>101000131,101000132</t>
-  </si>
-  <si>
-    <t>101001121,101001122</t>
-  </si>
-  <si>
-    <t>101001131,101001132</t>
+    <t>101001121,101001122,101001123</t>
   </si>
 </sst>
 </file>
@@ -577,7 +556,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -596,21 +575,6 @@
         <color theme="0"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -735,7 +699,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -747,34 +711,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -8064,524 +8028,524 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -8596,9 +8560,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -11281,7 +11242,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{3965249A-5260-4B32-80E5-3C4B15C413BA}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{D5399C9C-DA2C-4A29-8431-3F8EAFFD8422}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11581,20 +11542,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.75" customWidth="1"/>
     <col min="2" max="2" width="22.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.125" customWidth="1"/>
-    <col min="4" max="4" width="43.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.125" customWidth="1"/>
-    <col min="6" max="6" width="43.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="25.125" customWidth="1"/>
-    <col min="8" max="8" width="43.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="43.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="43.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -11607,101 +11564,59 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:4">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>7</v>
+      <c r="D2" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:8">
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>13</v>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:4">
       <c r="B4" s="2">
         <v>1010001</v>
       </c>
-      <c r="D4" s="2">
-        <v>101000111</v>
+      <c r="C4" s="6" t="s">
+        <v>10</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>18</v>
+      <c r="D4" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:4">
       <c r="B5" s="2">
         <v>1010011</v>
       </c>
-      <c r="D5" s="2">
-        <v>101001111</v>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>20</v>
+      <c r="D5" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="F8" s="7"/>
+    <row r="8" spans="1:4">
+      <c r="D8" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/SkillAugmentOptionsConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillAugmentOptionsConfig.xlsx
@@ -64,16 +64,16 @@
     <t>第2个技能增幅Ids</t>
   </si>
   <si>
-    <t>101000111,101000112</t>
+    <t>111000111,111000112</t>
   </si>
   <si>
-    <t>101000121,101000122,101000123</t>
+    <t>111000121,111000122,111000123</t>
   </si>
   <si>
-    <t>101001111,101001112</t>
+    <t>111001111,111001112</t>
   </si>
   <si>
-    <t>101001121,101001122,101001123</t>
+    <t>111001121,111001122,111001123</t>
   </si>
 </sst>
 </file>
@@ -11242,7 +11242,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{D5399C9C-DA2C-4A29-8431-3F8EAFFD8422}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{8E9D3506-82ED-4C0E-B4A1-4B0B987CAC52}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11595,7 +11595,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="B4" s="2">
-        <v>1010001</v>
+        <v>1110001</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>10</v>
@@ -11606,7 +11606,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="2">
-        <v>1010011</v>
+        <v>1110011</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>12</v>

--- a/Unity/Assets/Config/Excel/SkillAugmentOptionsConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillAugmentOptionsConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
   <si>
     <t>##var</t>
   </si>
@@ -11242,7 +11242,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{8E9D3506-82ED-4C0E-B4A1-4B0B987CAC52}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{92D67A49-5C2C-43BE-B69A-0E2D016D1F45}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -11542,8 +11542,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.75" customWidth="1"/>
     <col min="2" max="2" width="22.5" style="2" customWidth="1"/>
@@ -11615,8 +11615,71 @@
         <v>13</v>
       </c>
     </row>
+    <row r="6" spans="1:4">
+      <c r="B6" s="2">
+        <v>1110021</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" s="2">
+        <v>1110031</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="8" spans="1:4">
-      <c r="D8" s="6"/>
+      <c r="B8" s="2">
+        <v>1120001</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" s="2">
+        <v>1120011</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" s="2">
+        <v>1120021</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" s="2">
+        <v>1120031</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
